--- a/public/docs/exemplaires-import-biens/exemplaire_tranches_blocs_immeubles_old.xlsx
+++ b/public/docs/exemplaires-import-biens/exemplaire_tranches_blocs_immeubles_old.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5457185A-F3C4-433E-8149-63401D41A90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8616"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>RDC</t>
   </si>
@@ -190,12 +191,18 @@
   </si>
   <si>
     <t>2eme etage</t>
+  </si>
+  <si>
+    <t>Typologie</t>
+  </si>
+  <si>
+    <t>Vue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -343,7 +350,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
@@ -358,7 +365,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,39 +645,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" customWidth="1"/>
-    <col min="9" max="9" width="21.77734375" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" customWidth="1"/>
+    <col min="9" max="9" width="21.81640625" customWidth="1"/>
+    <col min="10" max="10" width="23.36328125" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="12.81640625" customWidth="1"/>
     <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="19.21875" customWidth="1"/>
-    <col min="16" max="16" width="17.5546875" customWidth="1"/>
-    <col min="17" max="17" width="16.21875" customWidth="1"/>
-    <col min="18" max="18" width="14.21875" customWidth="1"/>
-    <col min="19" max="19" width="12.109375" customWidth="1"/>
-    <col min="20" max="20" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.1796875" customWidth="1"/>
+    <col min="16" max="16" width="17.54296875" customWidth="1"/>
+    <col min="17" max="17" width="16.1796875" customWidth="1"/>
+    <col min="18" max="18" width="14.1796875" customWidth="1"/>
+    <col min="19" max="19" width="12.08984375" customWidth="1"/>
+    <col min="20" max="20" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
-    <col min="22" max="22" width="18.5546875" customWidth="1"/>
+    <col min="22" max="22" width="18.54296875" customWidth="1"/>
     <col min="23" max="23" width="19" customWidth="1"/>
-    <col min="24" max="25" width="17.88671875" customWidth="1"/>
+    <col min="24" max="25" width="17.90625" customWidth="1"/>
     <col min="26" max="27" width="19" customWidth="1"/>
-    <col min="28" max="30" width="17.88671875" customWidth="1"/>
+    <col min="28" max="30" width="17.90625" customWidth="1"/>
     <col min="31" max="31" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -767,8 +774,14 @@
       <c r="AF1" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -819,7 +832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -873,7 +886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" s="16" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" s="16" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="16" t="s">
         <v>7</v>
       </c>
@@ -930,7 +943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -985,7 +998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1042,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1099,7 +1112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1156,7 +1169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
